--- a/光伏配储项目/电价数据/2026/古坑站.xlsx
+++ b/光伏配储项目/电价数据/2026/古坑站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.41903</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.62997</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5878099999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45752</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41903</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42605</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49889</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.11283</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12387</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13147</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.06075999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10233</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.71166</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.23181</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.7652100000000001</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14623</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21682</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22772</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23272</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21696</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.46114</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1392</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.66912</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.7831399999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.87321</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.56878</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7313999999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.15733</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.44322</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43663</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65861</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.93131</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53947</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.26677</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.12362</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34798</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.50656</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75039</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.81186</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.46858</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87415</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7968999999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75746</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47995</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46808</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42561</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70956</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77994</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8737699999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9194</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49538</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51586</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50345</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5036700000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48591</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.9044099999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7462000000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.84199</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.44293</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50852</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49588</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76575</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.97923</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.50919</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8716</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.83026</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.48346</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70965</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.01666</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.04065</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.00493</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46178</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.53926</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.51583</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.95639</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.61766</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.07307</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.69107</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.16925</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.30427</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.75967</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.69147</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.74447</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.30199</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.63712</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90383</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.76731</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.6192</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.37973</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80502</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44932</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33464</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50841</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48762</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44364</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44422</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4383</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.6057899999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.17638</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.40783</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1.2614</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.20739</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.02331</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6214400000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.53835</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.47637</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.79706</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.57424</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7113700000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8010900000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52158</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.56153</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79606</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.43584</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.20992</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5888300000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49204</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42604</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52991</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50108</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56902</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5930599999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.55589</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26791</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6170399999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46817</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5535399999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5952000000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.20114</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.32199</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.4078</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.19655</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.05869</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.8420700000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.22375</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61136</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.06932</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56241</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.6688</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.01937</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5561499999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.47657</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61051</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.54486</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45698</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.59162</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.99607</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.83993</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.20439</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.74807</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.09797</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.3681</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.9645900000000001</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.71458</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.62546</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.57483</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1.34418</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6075900000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.46648</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47718</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.39293</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>1.38582</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.18665</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46262</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47472</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34046</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.26495</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.35542</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.1807</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50139</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.07491</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.00426</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.82382</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.68691</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.66806</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31813</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.84868</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.03321</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.18654</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.24816</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14789</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.00505</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.22023</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18568</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.04947</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.03775999999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22205</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.21025</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.20351</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06143</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.00313</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.01881</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00062</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.90803</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46358</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.49162</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3467</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.61348</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10264</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04349</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21291</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19691</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.04449</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.00226</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06705</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06528</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33294</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31489</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78527</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.70074</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.56343</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39989</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20699</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44984</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.56921</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58892</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.71839</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87797</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46738</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5629700000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.83966</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5922000000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85549</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87499</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6544099999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6492899999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5921000000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34962</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91562</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4763</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18063</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.55755</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.87621</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44815</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14853</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69231</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78286</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64389</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.53422</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.4947</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43449</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40942</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.47738</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.43027</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.53432</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.25847</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24895</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15479</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01267</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25408</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39382</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.55335</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.44444</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.80949</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44701</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31376</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22767</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17501</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.19688</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.21057</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.18046</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.19797</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.18942</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.16102</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.16482</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20224</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.16617</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.18182</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44015</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34002</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.50956</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.44829</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.78507</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.21066</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24863</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.65099</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.71109</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.77044</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6662</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.47675</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.20188</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.26372</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45695</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.45686</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>1.22602</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.61374</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.03756</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.65665</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.49114</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.49127</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.94774</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.56598</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.47256</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35317</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.47762</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.45653</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.54308</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.52758</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.68801</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.48054</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.39248</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.05929</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.56249</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5457799999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01863</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.5157200000000001</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.22521</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.09882</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.1363</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.46565</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6907000000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.85789</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.77189</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.65877</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29108</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.70926</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.7624</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.3976</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.78018</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.38026</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.00945</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.77542</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.01881</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.9838600000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.07338</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.99712</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.99438</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.68923</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.12116</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.10214</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.08404</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.35825</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.03031</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.69984</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.64095</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.54152</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50612</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24421</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.16594</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32323</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.36672</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.59075</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1.13446</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.62296</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.49624</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.62229</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>1.21338</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>1.21634</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34574</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.88136</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.61539</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.61541</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.66828</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45693</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.58908</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.46292</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.75387</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.93825</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.7374400000000001</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>1.09096</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.83847</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33831</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.56994</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.19917</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.7555599999999999</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.36645</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.9071399999999999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.42275</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.43398</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.9340900000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.51105</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>1.01213</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.7172500000000001</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>1.26355</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.04932</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.95904</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.93828</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.33849</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.96927</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.33824</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.27133</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.22912</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.18865</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.27488</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.20623</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.1158</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.02721</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.96733</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3549</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.46856</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.54757</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.49027</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6456799999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42863</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5261399999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.47579</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.43265</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.6588099999999999</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.69951</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.28868</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.74671</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.78332</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.24406</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.26628</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.59488</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.6665</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.01021</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.47245</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48895</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48935</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.52567</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6557200000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7755</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.86807</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.62437</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7516900000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59348</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7744</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7671699999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62012</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66871</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46238</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.45792</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45093</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40559</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.52488</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42059</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5053299999999999</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.38282</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>1.18265</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.13647</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.34634</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.20252</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.22507</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.20349</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23889</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.11426</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2545</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03803</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28065</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18402</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18492</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24279</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23786</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.54187</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33474</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.26961</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.26782</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.26939</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23219</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01488</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-5.999999999999999e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14695</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01526</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04079</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04825</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02927</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04842</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27521</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03791</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01812</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03604</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20224</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26552</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33972</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.78096</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6724199999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.47298</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.44159</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43975</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.7610399999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.89479</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.88073</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8539800000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11773</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24269</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.01028</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27292</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00184</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05974</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25414</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47156</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.57146</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.8125399999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.79447</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.79788</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.38635</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97727</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.79474</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.82708</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8421900000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.84039</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8446699999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94178</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.79059</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8230299999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7927799999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36945</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.48003</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6379400000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.7360599999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5982000000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49606</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.47761</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.49329</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47711</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.49304</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15015</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.16854</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.16681</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.14106</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.16537</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.16359</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.16887</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.17273</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1.17375</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26147</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.17404</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.31782</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>1.17956</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>1.17343</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>1.17566</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>1.17161</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.68426</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>1.17155</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17649</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.78332</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6782</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42668</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7748700000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47152</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.49673</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.346</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43471</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.79397</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.57183</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.49729</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.15169</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.17364</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.1677</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.17182</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.24386</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.15731</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.78143</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.17199</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.17505</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.16311</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.04655</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.16148</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.20896</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.45341</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6570499999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.18337</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.15571</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.13952</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.13312</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.15085</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.66335</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.68738</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.22221</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>1.15959</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24091</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46334</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.78926</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.79755</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.03983</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.21723</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.78767</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.8959900000000001</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51112</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.47513</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.9805700000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.00933</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.15094</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.20331</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.9670299999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.83157</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.48789</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.68803</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.76719</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6970700000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.79512</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36304</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.37381</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.33816</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.35432</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.68192</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.51859</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.51635</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.55926</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.56002</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.68775</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.17084</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.57482</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.5731900000000001</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5305299999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.08029</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.21662</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.18625</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.03929</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.21315</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>-0.03305</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.23349</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.52519</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.5286000000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.52695</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.5638300000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.69062</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.6892200000000001</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.14595</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.17283</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.68708</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.17012</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.11049</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.50264</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16356</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.16753</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.16911</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.16938</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.5506799999999999</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.51719</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.18741</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37044</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.87919</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.22667</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56424</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.21096</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1.44737</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.16776</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.36615</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.3599</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.17661</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.73997</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.17806</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.17578</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.49469</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.6849700000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.84124</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.0805</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.72421</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.32242</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.22767</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.7104299999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.36824</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.30862</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.32325</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1.33356</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.35027</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.16844</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.19212</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.19057</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1.17329</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.25266</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.19257</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.19494</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17703</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.18139</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.19021</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.5241</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.5664199999999999</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.69738</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.18952</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.31916</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.31377</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.35256</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.38811</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.34659</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.38432</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.14264</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.9268</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.14995</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.52726</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.5827599999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.65179</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.73933</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3624</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17571</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14539</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19811</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14154</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04471</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12023</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22396</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14903</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14316</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19374</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22628</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26302</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15356</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15371</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19728</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19016</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.16878</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.25268</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.05806</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38705</v>
       </c>
     </row>
   </sheetData>
